--- a/4_outputs/final/Table19.xlsx
+++ b/4_outputs/final/Table19.xlsx
@@ -423,9 +423,9 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.995</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.966</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.755</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.681</t>
         </is>
       </c>
     </row>

--- a/4_outputs/final/Table19.xlsx
+++ b/4_outputs/final/Table19.xlsx
@@ -417,15 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,259 +436,307 @@
           <t>SDG</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Segment cap</t>
-        </is>
-      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Encoder (embedding architecture)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr"/>
       <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval</t>
-        </is>
-      </c>
+      <c r="E1" s="1" t="inlineStr"/>
       <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Canon</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+          <t>MPNet (768-d)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
+          <t>MiniLM (384-d)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SciBERT (768-d)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>LR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>MLP</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MLP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>17</t>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -696,29 +746,39 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -728,327 +788,479 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Rank Corr (ρ)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0.995</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0.966</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.755</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0.681</t>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.863</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.534</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.400</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.373</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.463</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.618</t>
         </is>
       </c>
     </row>
